--- a/data_lake/datos_diarios_preliminares/dt=2026-07-23/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-23/temperaturamed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F5153D-CD39-479A-9486-BA8A91C87A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B7D5E2-9601-434D-9EE2-40515CC61DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Temperatura" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AE$1:$AE$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AF$1:$AF$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="108" width="32.42578125" style="50" customWidth="1"/>
-    <col min="109" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="109" width="32.42578125" style="50" customWidth="1"/>
+    <col min="110" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6701,7 +6701,9 @@
       <c r="AE5" s="56">
         <v>28.8</v>
       </c>
-      <c r="AF5" s="56"/>
+      <c r="AF5" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AG5" s="56"/>
       <c r="AH5" s="56"/>
       <c r="AI5" s="56"/>
@@ -6713,11 +6715,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.833333333333332</v>
+        <v>28.831818181818178</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6725,7 +6727,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.68011844436206204</v>
+        <v>0.67860329284690835</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6822,7 +6824,9 @@
       <c r="AE6" s="56">
         <v>28.7</v>
       </c>
-      <c r="AF6" s="56"/>
+      <c r="AF6" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AG6" s="56"/>
       <c r="AH6" s="56"/>
       <c r="AI6" s="56"/>
@@ -6834,11 +6838,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.857142857142858</v>
+        <v>28.877272727272725</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6846,7 +6850,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.46190896819403804</v>
+        <v>0.48203883832390559</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6943,7 +6947,9 @@
       <c r="AE7" s="56">
         <v>29.1</v>
       </c>
-      <c r="AF7" s="56"/>
+      <c r="AF7" s="56">
+        <v>32.1</v>
+      </c>
       <c r="AG7" s="56"/>
       <c r="AH7" s="56"/>
       <c r="AI7" s="56"/>
@@ -6955,11 +6961,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.647619047619049</v>
+        <v>31.668181818181822</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6967,7 +6973,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.4474385560675884</v>
+        <v>2.4680013266303611</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7064,7 +7070,9 @@
       <c r="AE8" s="56">
         <v>29</v>
       </c>
-      <c r="AF8" s="56"/>
+      <c r="AF8" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AG8" s="56"/>
       <c r="AH8" s="56"/>
       <c r="AI8" s="56"/>
@@ -7076,11 +7084,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.861904761904764</v>
+        <v>29.831818181818186</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7088,7 +7096,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.283365445733363</v>
+        <v>1.2532788656467844</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7185,7 +7193,9 @@
       <c r="AE9" s="56">
         <v>29.1</v>
       </c>
-      <c r="AF9" s="56"/>
+      <c r="AF9" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AG9" s="56"/>
       <c r="AH9" s="56"/>
       <c r="AI9" s="56"/>
@@ -7197,11 +7207,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.452380952380953</v>
+        <v>29.436363636363637</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7209,7 +7219,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.33508803024927758</v>
+        <v>-0.35110534626659273</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7306,7 +7316,9 @@
       <c r="AE10" s="56">
         <v>32.5</v>
       </c>
-      <c r="AF10" s="56"/>
+      <c r="AF10" s="56">
+        <v>30</v>
+      </c>
       <c r="AG10" s="56"/>
       <c r="AH10" s="56"/>
       <c r="AI10" s="56"/>
@@ -7318,11 +7330,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.852380952380951</v>
+        <v>31.768181818181816</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7330,7 +7342,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.7729589179758918</v>
+        <v>1.6887597837767565</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7427,7 +7439,9 @@
       <c r="AE11" s="56">
         <v>31.5</v>
       </c>
-      <c r="AF11" s="56"/>
+      <c r="AF11" s="56">
+        <v>31.7</v>
+      </c>
       <c r="AG11" s="56"/>
       <c r="AH11" s="56"/>
       <c r="AI11" s="56"/>
@@ -7439,11 +7453,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.842857142857142</v>
+        <v>32.790909090909089</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7451,7 +7465,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.8389430656292909</v>
+        <v>2.7869950136812385</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7548,7 +7562,9 @@
       <c r="AE12" s="56">
         <v>30</v>
       </c>
-      <c r="AF12" s="56"/>
+      <c r="AF12" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AG12" s="56"/>
       <c r="AH12" s="56"/>
       <c r="AI12" s="56"/>
@@ -7560,11 +7576,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.309523809523803</v>
+        <v>30.318181818181813</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7572,7 +7588,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>2.0438574202082229</v>
+        <v>2.0525154288662328</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7669,7 +7685,9 @@
       <c r="AE13" s="56">
         <v>27.6</v>
       </c>
-      <c r="AF13" s="56"/>
+      <c r="AF13" s="56">
+        <v>29.9</v>
+      </c>
       <c r="AG13" s="56"/>
       <c r="AH13" s="56"/>
       <c r="AI13" s="56"/>
@@ -7681,11 +7699,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>30.099999999999994</v>
+        <v>30.090909090909086</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7693,7 +7711,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.7706053021876329</v>
+        <v>1.761514393096725</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7790,7 +7808,9 @@
       <c r="AE14" s="56">
         <v>22</v>
       </c>
-      <c r="AF14" s="56"/>
+      <c r="AF14" s="56">
+        <v>24.7</v>
+      </c>
       <c r="AG14" s="56"/>
       <c r="AH14" s="56"/>
       <c r="AI14" s="56"/>
@@ -7802,11 +7822,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.709523809523805</v>
+        <v>23.75454545454545</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7814,7 +7834,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.9879837856289555</v>
+        <v>2.0330054306506007</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7911,7 +7931,9 @@
       <c r="AE15" s="56">
         <v>29.1</v>
       </c>
-      <c r="AF15" s="56"/>
+      <c r="AF15" s="56">
+        <v>31.3</v>
+      </c>
       <c r="AG15" s="56"/>
       <c r="AH15" s="56"/>
       <c r="AI15" s="56"/>
@@ -7923,11 +7945,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.033333333333335</v>
+        <v>29.136363636363637</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7935,7 +7957,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.79782795698925568</v>
+        <v>0.90085826001955738</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8032,7 +8054,9 @@
       <c r="AE16" s="56">
         <v>28.4</v>
       </c>
-      <c r="AF16" s="56"/>
+      <c r="AF16" s="56">
+        <v>29</v>
+      </c>
       <c r="AG16" s="56"/>
       <c r="AH16" s="56"/>
       <c r="AI16" s="56"/>
@@ -8044,11 +8068,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.495238095238093</v>
+        <v>28.518181818181816</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8056,7 +8080,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.85758524683511439</v>
+        <v>0.88052896977883677</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8153,7 +8177,9 @@
       <c r="AE17" s="56">
         <v>25.1</v>
       </c>
-      <c r="AF17" s="56"/>
+      <c r="AF17" s="56">
+        <v>23.6</v>
+      </c>
       <c r="AG17" s="56"/>
       <c r="AH17" s="56"/>
       <c r="AI17" s="56"/>
@@ -8165,11 +8191,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.87619047619048</v>
+        <v>24.818181818181824</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8177,7 +8203,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.8925668070342816</v>
+        <v>0.83455814902562508</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8274,7 +8300,9 @@
       <c r="AE18" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="AF18" s="56"/>
+      <c r="AF18" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="AG18" s="56"/>
       <c r="AH18" s="56"/>
       <c r="AI18" s="56"/>
@@ -8286,11 +8314,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.761904761904763</v>
+        <v>18.754545454545454</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8298,7 +8326,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3435535074244811</v>
+        <v>1.3361942000651723</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8395,7 +8423,9 @@
       <c r="AE19" s="56">
         <v>24.4</v>
       </c>
-      <c r="AF19" s="56"/>
+      <c r="AF19" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AG19" s="56"/>
       <c r="AH19" s="56"/>
       <c r="AI19" s="56"/>
@@ -8407,11 +8437,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.452380952380953</v>
+        <v>24.486363636363638</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8419,7 +8449,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.3188460061444012</v>
+        <v>2.3528286901270867</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8516,7 +8546,9 @@
       <c r="AE20" s="56">
         <v>23.6</v>
       </c>
-      <c r="AF20" s="56"/>
+      <c r="AF20" s="56">
+        <v>22.4</v>
+      </c>
       <c r="AG20" s="56"/>
       <c r="AH20" s="56"/>
       <c r="AI20" s="56"/>
@@ -8528,11 +8560,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.404761904761905</v>
+        <v>24.313636363636363</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8540,7 +8572,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.797096478790035</v>
+        <v>1.7059709376644925</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8637,7 +8669,9 @@
       <c r="AE21" s="56">
         <v>26.6</v>
       </c>
-      <c r="AF21" s="56"/>
+      <c r="AF21" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AG21" s="56"/>
       <c r="AH21" s="56"/>
       <c r="AI21" s="56"/>
@@ -8649,11 +8683,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.11904761904762</v>
+        <v>27.181818181818183</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8661,7 +8695,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.428965727290489</v>
+        <v>2.491736290061052</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8758,7 +8792,9 @@
       <c r="AE22" s="56">
         <v>15.4</v>
       </c>
-      <c r="AF22" s="56"/>
+      <c r="AF22" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AG22" s="56"/>
       <c r="AH22" s="56"/>
       <c r="AI22" s="56"/>
@@ -8770,11 +8806,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.476190476190473</v>
+        <v>15.527272727272726</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8782,7 +8818,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.695857556422073</v>
+        <v>1.7469398075043259</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8879,7 +8915,9 @@
       <c r="AE23" s="56">
         <v>26.3</v>
       </c>
-      <c r="AF23" s="56"/>
+      <c r="AF23" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AG23" s="56"/>
       <c r="AH23" s="56"/>
       <c r="AI23" s="56"/>
@@ -8891,11 +8929,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.176190476190467</v>
+        <v>26.190909090909084</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9000,7 +9038,9 @@
       <c r="AE24" s="56">
         <v>30.5</v>
       </c>
-      <c r="AF24" s="56"/>
+      <c r="AF24" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AG24" s="56"/>
       <c r="AH24" s="56"/>
       <c r="AI24" s="56"/>
@@ -9012,11 +9052,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.328571428571433</v>
+        <v>29.38636363636364</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9024,7 +9064,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>0.96621294383531264</v>
+        <v>1.0240051516275201</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9121,7 +9161,9 @@
       <c r="AE25" s="56">
         <v>19.5</v>
       </c>
-      <c r="AF25" s="56"/>
+      <c r="AF25" s="56">
+        <v>22.1</v>
+      </c>
       <c r="AG25" s="56"/>
       <c r="AH25" s="56"/>
       <c r="AI25" s="56"/>
@@ -9133,11 +9175,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.93333333333333</v>
+        <v>21.940909090909088</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9145,7 +9187,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.99990887713113</v>
+        <v>2.0074846347068878</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9242,7 +9284,9 @@
       <c r="AE26" s="56">
         <v>11.7</v>
       </c>
-      <c r="AF26" s="56"/>
+      <c r="AF26" s="56">
+        <v>12.1</v>
+      </c>
       <c r="AG26" s="56"/>
       <c r="AH26" s="56"/>
       <c r="AI26" s="56"/>
@@ -9254,11 +9298,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.671428571428569</v>
+        <v>11.690909090909088</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9266,7 +9310,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.3011136712749796</v>
+        <v>1.3205941907554983</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9363,7 +9407,9 @@
       <c r="AE27" s="56">
         <v>27.6</v>
       </c>
-      <c r="AF27" s="56"/>
+      <c r="AF27" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AG27" s="56"/>
       <c r="AH27" s="56"/>
       <c r="AI27" s="56"/>
@@ -9375,11 +9421,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.161904761904761</v>
+        <v>28.136363636363637</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9387,7 +9433,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.1731987923089129</v>
+        <v>1.1476576667677882</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9484,7 +9530,9 @@
       <c r="AE28" s="56">
         <v>27.2</v>
       </c>
-      <c r="AF28" s="56"/>
+      <c r="AF28" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AG28" s="56"/>
       <c r="AH28" s="56"/>
       <c r="AI28" s="56"/>
@@ -9496,11 +9544,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.62857142857143</v>
+        <v>26.563636363636366</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9508,7 +9556,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.8771528770944883</v>
+        <v>0.81221781215942457</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9605,7 +9653,9 @@
       <c r="AE29" s="56">
         <v>29</v>
       </c>
-      <c r="AF29" s="56"/>
+      <c r="AF29" s="56">
+        <v>28.2</v>
+      </c>
       <c r="AG29" s="56"/>
       <c r="AH29" s="56"/>
       <c r="AI29" s="56"/>
@@ -9617,11 +9667,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.647619047619049</v>
+        <v>27.672727272727276</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9629,7 +9679,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.69357683336180997</v>
+        <v>0.71868505847003661</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9726,7 +9776,9 @@
       <c r="AE30" s="56">
         <v>26</v>
       </c>
-      <c r="AF30" s="56"/>
+      <c r="AF30" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AG30" s="56"/>
       <c r="AH30" s="56"/>
       <c r="AI30" s="56"/>
@@ -9738,11 +9790,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.161904761904761</v>
+        <v>25.204545454545453</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9750,7 +9802,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.64390327877539022</v>
+        <v>0.68654397141608214</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9847,7 +9899,9 @@
       <c r="AE31" s="98">
         <v>28</v>
       </c>
-      <c r="AF31" s="98"/>
+      <c r="AF31" s="98">
+        <v>27.9</v>
+      </c>
       <c r="AG31" s="98"/>
       <c r="AH31" s="98"/>
       <c r="AI31" s="98"/>
@@ -9859,11 +9913,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.81428571428571</v>
+        <v>26.86363636363636</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9871,7 +9925,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4453370882403114</v>
+        <v>1.4946877375909615</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9954,13 +10008,13 @@
         <v>19.866666666666671</v>
       </c>
       <c r="AA32" s="56">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB32" s="56">
         <v>20.266666666666669</v>
       </c>
       <c r="AC32" s="56">
-        <v>20.966666666666669</v>
+        <v>21.13333333333334</v>
       </c>
       <c r="AD32" s="56">
         <v>20.533333333333331</v>
@@ -9968,7 +10022,9 @@
       <c r="AE32" s="56">
         <v>20.6</v>
       </c>
-      <c r="AF32" s="56"/>
+      <c r="AF32" s="56">
+        <v>20.666666666666671</v>
+      </c>
       <c r="AG32" s="56"/>
       <c r="AH32" s="56"/>
       <c r="AI32" s="56"/>
@@ -9980,11 +10036,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.579365079365079</v>
+        <v>20.595454545454547</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9992,7 +10048,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.9225090272562397</v>
+        <v>2.9385984933457081</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10086,8 +10142,12 @@
       <c r="AD33" s="56">
         <v>27.75</v>
       </c>
-      <c r="AE33" s="56"/>
-      <c r="AF33" s="56"/>
+      <c r="AE33" s="56">
+        <v>27.45</v>
+      </c>
+      <c r="AF33" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AG33" s="56"/>
       <c r="AH33" s="56"/>
       <c r="AI33" s="56"/>
@@ -10099,11 +10159,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>28.052499999999998</v>
+        <v>28.040909090909089</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10111,7 +10171,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.2250279187874469</v>
+        <v>1.2134370096965377</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10208,7 +10268,9 @@
       <c r="AE34" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AF34" s="56"/>
+      <c r="AF34" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AG34" s="56"/>
       <c r="AH34" s="56"/>
       <c r="AI34" s="56"/>
@@ -10220,11 +10282,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.349206349206352</v>
+        <v>21.354545454545459</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10232,7 +10294,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.56200875752603</v>
+        <v>1.5673478628651374</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10329,7 +10391,9 @@
       <c r="AE35" s="56">
         <v>24</v>
       </c>
-      <c r="AF35" s="56"/>
+      <c r="AF35" s="56">
+        <v>24.55</v>
+      </c>
       <c r="AG35" s="56"/>
       <c r="AH35" s="56"/>
       <c r="AI35" s="56"/>
@@ -10341,11 +10405,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.654761904761905</v>
+        <v>24.65</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10353,7 +10417,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.61651400504450393</v>
+        <v>0.61175210028259741</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10450,7 +10514,9 @@
       <c r="AE36" s="56">
         <v>18.75</v>
       </c>
-      <c r="AF36" s="56"/>
+      <c r="AF36" s="56">
+        <v>21.05</v>
+      </c>
       <c r="AG36" s="56"/>
       <c r="AH36" s="56"/>
       <c r="AI36" s="56"/>
@@ -10462,11 +10528,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>20.092857142857145</v>
+        <v>20.13636363636364</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10474,7 +10540,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.0940460796387548</v>
+        <v>1.1375525731452498</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10571,7 +10637,9 @@
       <c r="AE37" s="56">
         <v>27.2</v>
       </c>
-      <c r="AF37" s="56"/>
+      <c r="AF37" s="56">
+        <v>28.25</v>
+      </c>
       <c r="AG37" s="56"/>
       <c r="AH37" s="56"/>
       <c r="AI37" s="56"/>
@@ -10583,11 +10651,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.459523809523812</v>
+        <v>27.49545454545455</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10595,7 +10663,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.573293935586431</v>
+        <v>1.6092246715171683</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10807,7 +10875,9 @@
       <c r="AE39" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="AF39" s="56"/>
+      <c r="AF39" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AG39" s="56"/>
       <c r="AH39" s="56"/>
       <c r="AI39" s="56"/>
@@ -10819,11 +10889,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.563333333333336</v>
+        <v>22.526984126984129</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10918,7 +10988,9 @@
       </c>
       <c r="AD40" s="56"/>
       <c r="AE40" s="56"/>
-      <c r="AF40" s="56"/>
+      <c r="AF40" s="56">
+        <v>25.15</v>
+      </c>
       <c r="AG40" s="56"/>
       <c r="AH40" s="56"/>
       <c r="AI40" s="56"/>
@@ -10930,11 +11002,11 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.462499999999999</v>
+        <v>25.444117647058821</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10942,7 +11014,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.6107092515730272</v>
+        <v>2.5923268986318497</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11037,7 +11109,9 @@
       <c r="AE41" s="56">
         <v>19.8</v>
       </c>
-      <c r="AF41" s="56"/>
+      <c r="AF41" s="56">
+        <v>18.8</v>
+      </c>
       <c r="AG41" s="56"/>
       <c r="AH41" s="56"/>
       <c r="AI41" s="56"/>
@@ -11049,11 +11123,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.441666666666663</v>
+        <v>20.36349206349206</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11061,7 +11135,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.9495574753389242</v>
+        <v>1.8713828721643218</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11158,7 +11232,9 @@
       <c r="AE42" s="56">
         <v>27.824999999999999</v>
       </c>
-      <c r="AF42" s="56"/>
+      <c r="AF42" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AG42" s="56"/>
       <c r="AH42" s="56"/>
       <c r="AI42" s="56"/>
@@ -11170,11 +11246,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>28.151190476190475</v>
+        <v>28.171590909090909</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11182,7 +11258,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.39850495913220385</v>
+        <v>0.41890539203263799</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11275,7 +11351,9 @@
       <c r="AE43" s="56">
         <v>28.85</v>
       </c>
-      <c r="AF43" s="56"/>
+      <c r="AF43" s="56">
+        <v>29.85</v>
+      </c>
       <c r="AG43" s="56"/>
       <c r="AH43" s="56"/>
       <c r="AI43" s="56"/>
@@ -11287,11 +11365,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.542105263157897</v>
+        <v>29.557500000000005</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11396,7 +11474,9 @@
       <c r="AE44" s="56">
         <v>28.45</v>
       </c>
-      <c r="AF44" s="56"/>
+      <c r="AF44" s="56">
+        <v>28.425000000000001</v>
+      </c>
       <c r="AG44" s="56"/>
       <c r="AH44" s="56"/>
       <c r="AI44" s="56"/>
@@ -11408,11 +11488,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.609523809523807</v>
+        <v>28.60113636363636</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11420,7 +11500,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.2671803652409857</v>
+        <v>1.2587929193535388</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11517,7 +11597,9 @@
       <c r="AE45" s="56">
         <v>27.95</v>
       </c>
-      <c r="AF45" s="56"/>
+      <c r="AF45" s="56">
+        <v>29.65</v>
+      </c>
       <c r="AG45" s="56"/>
       <c r="AH45" s="56"/>
       <c r="AI45" s="56"/>
@@ -11529,11 +11611,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.480952380952388</v>
+        <v>29.48863636363637</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11541,7 +11623,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.7128449060209583</v>
+        <v>1.7205288887049406</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11638,7 +11720,9 @@
       <c r="AE46" s="56">
         <v>28.9</v>
       </c>
-      <c r="AF46" s="56"/>
+      <c r="AF46" s="56">
+        <v>28.55</v>
+      </c>
       <c r="AG46" s="56"/>
       <c r="AH46" s="56"/>
       <c r="AI46" s="56"/>
@@ -11650,11 +11734,11 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>29.034523809523812</v>
+        <v>29.012499999999999</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11662,7 +11746,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.1283261776263309</v>
+        <v>1.1063023681025186</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11759,7 +11843,9 @@
       <c r="AE47" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="AF47" s="56"/>
+      <c r="AF47" s="56">
+        <v>30.466666666666669</v>
+      </c>
       <c r="AG47" s="56"/>
       <c r="AH47" s="56"/>
       <c r="AI47" s="56"/>
@@ -11771,11 +11857,11 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>30.144444444444449</v>
+        <v>30.159090909090914</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11783,7 +11869,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>2.1755685851270599</v>
+        <v>2.1902150497735242</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12038,7 +12124,9 @@
       <c r="AE50" s="56">
         <v>28.25</v>
       </c>
-      <c r="AF50" s="56"/>
+      <c r="AF50" s="56">
+        <v>28.85</v>
+      </c>
       <c r="AG50" s="56"/>
       <c r="AH50" s="56"/>
       <c r="AI50" s="56"/>
@@ -12050,11 +12138,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.519047619047619</v>
+        <v>29.488636363636363</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12062,7 +12150,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>2.2303572730157981</v>
+        <v>2.1999460176045424</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12345,7 +12433,9 @@
       <c r="AE53" s="56">
         <v>27.75</v>
       </c>
-      <c r="AF53" s="56"/>
+      <c r="AF53" s="56">
+        <v>28.15</v>
+      </c>
       <c r="AG53" s="56"/>
       <c r="AH53" s="56"/>
       <c r="AI53" s="56"/>
@@ -12357,11 +12447,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>29.195238095238096</v>
+        <v>29.147727272727273</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12369,7 +12459,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.835991798647548</v>
+        <v>1.7884809761367251</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12466,7 +12556,9 @@
       <c r="AE54" s="56">
         <v>29.5</v>
       </c>
-      <c r="AF54" s="56"/>
+      <c r="AF54" s="56">
+        <v>31.2</v>
+      </c>
       <c r="AG54" s="56"/>
       <c r="AH54" s="56"/>
       <c r="AI54" s="56"/>
@@ -12478,11 +12570,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>30.295238095238098</v>
+        <v>30.33636363636364</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12490,7 +12582,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.7970120701716787</v>
+        <v>1.8381376112972205</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12573,7 +12665,9 @@
       <c r="AE55" s="56">
         <v>29</v>
       </c>
-      <c r="AF55" s="56"/>
+      <c r="AF55" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AG55" s="56"/>
       <c r="AH55" s="56"/>
       <c r="AI55" s="56"/>
@@ -12585,19 +12679,19 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ55" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.626666666666669</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.430959670237041</v>
       </c>
-      <c r="AS55" s="71" t="str">
+      <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.1957069964296281</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12973,7 +13067,9 @@
       <c r="AE59" s="56">
         <v>28.5</v>
       </c>
-      <c r="AF59" s="56"/>
+      <c r="AF59" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AG59" s="56"/>
       <c r="AH59" s="56"/>
       <c r="AI59" s="56"/>
@@ -12985,11 +13081,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.251190476190477</v>
+        <v>29.228409090909089</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12997,7 +13093,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>1.136970647108317</v>
+        <v>1.1141892618269296</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13209,7 +13305,9 @@
       <c r="AE61" s="56">
         <v>27.95</v>
       </c>
-      <c r="AF61" s="56"/>
+      <c r="AF61" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AG61" s="56"/>
       <c r="AH61" s="56"/>
       <c r="AI61" s="56"/>
@@ -13221,11 +13319,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.619047619047624</v>
+        <v>26.572727272727278</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13233,7 +13331,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>0.91237593732166289</v>
+        <v>0.86605559100131657</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13330,7 +13428,9 @@
       <c r="AE62" s="56">
         <v>26.6</v>
       </c>
-      <c r="AF62" s="56"/>
+      <c r="AF62" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AG62" s="56"/>
       <c r="AH62" s="56"/>
       <c r="AI62" s="56"/>
@@ -13342,11 +13442,11 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>25.841269841269845</v>
+        <v>25.875757575757579</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13354,7 +13454,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.3022659013059545</v>
+        <v>1.3367536357936878</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13576,8 +13676,12 @@
       <c r="Z65" s="56">
         <v>28.3</v>
       </c>
-      <c r="AA65" s="56"/>
-      <c r="AB65" s="56"/>
+      <c r="AA65" s="56">
+        <v>26.65</v>
+      </c>
+      <c r="AB65" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AC65" s="56">
         <v>24.8</v>
       </c>
@@ -13599,7 +13703,7 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ65" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13708,7 +13812,9 @@
       <c r="AE66" s="56">
         <v>25.4</v>
       </c>
-      <c r="AF66" s="56"/>
+      <c r="AF66" s="56">
+        <v>24.4</v>
+      </c>
       <c r="AG66" s="56"/>
       <c r="AH66" s="56"/>
       <c r="AI66" s="56"/>
@@ -13720,11 +13826,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.68095238095238</v>
+        <v>25.622727272727271</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13732,7 +13838,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.77183755067338922</v>
+        <v>0.71361244244828015</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13825,7 +13931,9 @@
       <c r="AE67" s="56">
         <v>26.45</v>
       </c>
-      <c r="AF67" s="56"/>
+      <c r="AF67" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AG67" s="56"/>
       <c r="AH67" s="56"/>
       <c r="AI67" s="56"/>
@@ -13837,11 +13945,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.371052631578944</v>
+        <v>25.4</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13849,7 +13957,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.71984571974773459</v>
+        <v>0.74879308816878876</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13946,7 +14054,9 @@
       <c r="AE68" s="56">
         <v>25.35</v>
       </c>
-      <c r="AF68" s="56"/>
+      <c r="AF68" s="56">
+        <v>27.15</v>
+      </c>
       <c r="AG68" s="56"/>
       <c r="AH68" s="56"/>
       <c r="AI68" s="56"/>
@@ -13958,11 +14068,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.328571428571429</v>
+        <v>25.411363636363635</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13970,7 +14080,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.80348392582840944</v>
+        <v>0.88627613362061552</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14067,7 +14177,9 @@
       <c r="AE69" s="56">
         <v>25.05</v>
       </c>
-      <c r="AF69" s="56"/>
+      <c r="AF69" s="56">
+        <v>23.75</v>
+      </c>
       <c r="AG69" s="56"/>
       <c r="AH69" s="56"/>
       <c r="AI69" s="56"/>
@@ -14079,11 +14191,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>25.030952380952378</v>
+        <v>24.972727272727273</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14091,7 +14203,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.70855469432036955</v>
+        <v>0.65032958609526403</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14174,7 +14286,9 @@
       <c r="AE70" s="56">
         <v>26.86666666666666</v>
       </c>
-      <c r="AF70" s="56"/>
+      <c r="AF70" s="56">
+        <v>26.13333333333334</v>
+      </c>
       <c r="AG70" s="56"/>
       <c r="AH70" s="56"/>
       <c r="AI70" s="56"/>
@@ -14186,19 +14300,19 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ70" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>26.451111111111111</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.569958691043201</v>
       </c>
-      <c r="AS70" s="71" t="str">
+      <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.8811524200679095</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14295,7 +14409,9 @@
       <c r="AE71" s="56">
         <v>26.433333333333341</v>
       </c>
-      <c r="AF71" s="56"/>
+      <c r="AF71" s="56">
+        <v>26.233333333333331</v>
+      </c>
       <c r="AG71" s="56"/>
       <c r="AH71" s="56"/>
       <c r="AI71" s="56"/>
@@ -14307,11 +14423,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.963492063492065</v>
+        <v>25.975757575757576</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14319,7 +14435,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.30104914983853703</v>
+        <v>0.31331466210404813</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14414,7 +14530,9 @@
       <c r="AE72" s="56">
         <v>26.233333333333331</v>
       </c>
-      <c r="AF72" s="56"/>
+      <c r="AF72" s="56">
+        <v>24.93333333333333</v>
+      </c>
       <c r="AG72" s="56"/>
       <c r="AH72" s="56"/>
       <c r="AI72" s="56"/>
@@ -14426,11 +14544,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.416666666666675</v>
+        <v>25.393650793650799</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14438,7 +14556,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.4434579237071361</v>
+        <v>0.4204420506912605</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14523,7 +14641,9 @@
       <c r="AE73" s="56">
         <v>26.45</v>
       </c>
-      <c r="AF73" s="56"/>
+      <c r="AF73" s="56">
+        <v>25.9</v>
+      </c>
       <c r="AG73" s="56"/>
       <c r="AH73" s="56"/>
       <c r="AI73" s="56"/>
@@ -14535,11 +14655,11 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.819999999999997</v>
+        <v>25.824999999999996</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14644,7 +14764,9 @@
       <c r="AE74" s="56">
         <v>22.05</v>
       </c>
-      <c r="AF74" s="56"/>
+      <c r="AF74" s="56">
+        <v>22.95</v>
+      </c>
       <c r="AG74" s="56"/>
       <c r="AH74" s="56"/>
       <c r="AI74" s="56"/>
@@ -14656,11 +14778,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.542857142857144</v>
+        <v>20.652272727272727</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14668,7 +14790,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.54435839349703485</v>
+        <v>0.65377397791261771</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14765,7 +14887,9 @@
       <c r="AE75" s="56">
         <v>17.266666666666669</v>
       </c>
-      <c r="AF75" s="56"/>
+      <c r="AF75" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="AG75" s="56"/>
       <c r="AH75" s="56"/>
       <c r="AI75" s="56"/>
@@ -14777,11 +14901,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.64603174603174</v>
+        <v>15.740909090909087</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14789,7 +14913,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.46498805406494981</v>
+        <v>0.55986539894229637</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14886,7 +15010,9 @@
       <c r="AE76" s="56">
         <v>22.85</v>
       </c>
-      <c r="AF76" s="56"/>
+      <c r="AF76" s="56">
+        <v>21.2</v>
+      </c>
       <c r="AG76" s="56"/>
       <c r="AH76" s="56"/>
       <c r="AI76" s="56"/>
@@ -14898,11 +15024,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.767857142857142</v>
+        <v>20.787499999999998</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14910,7 +15036,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.96789053133092295</v>
+        <v>0.98753338847377847</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15007,7 +15133,9 @@
       <c r="AE77" s="56">
         <v>25.333333333333329</v>
       </c>
-      <c r="AF77" s="56"/>
+      <c r="AF77" s="56">
+        <v>25</v>
+      </c>
       <c r="AG77" s="56"/>
       <c r="AH77" s="56"/>
       <c r="AI77" s="56"/>
@@ -15019,11 +15147,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>23.873015873015866</v>
+        <v>23.924242424242422</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15031,7 +15159,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.189775017036947</v>
+        <v>1.2410015682635027</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15128,7 +15256,9 @@
       <c r="AE78" s="56">
         <v>31.7</v>
       </c>
-      <c r="AF78" s="56"/>
+      <c r="AF78" s="56">
+        <v>32.349999999999987</v>
+      </c>
       <c r="AG78" s="56"/>
       <c r="AH78" s="56"/>
       <c r="AI78" s="56"/>
@@ -15140,11 +15270,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.078571428571422</v>
+        <v>31.13636363636363</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15152,7 +15282,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.8946416180487731</v>
+        <v>1.9524338258409806</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15218,7 +15348,9 @@
       </c>
       <c r="U79" s="56"/>
       <c r="V79" s="56"/>
-      <c r="W79" s="56"/>
+      <c r="W79" s="56">
+        <v>30.733333333333331</v>
+      </c>
       <c r="X79" s="56">
         <v>29.93333333333333</v>
       </c>
@@ -15255,11 +15387,11 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.055555555555557</v>
+        <v>31.03859649122807</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15267,7 +15399,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.586502671104828</v>
+        <v>1.5695436067773407</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15358,7 +15490,9 @@
       <c r="AC80" s="56">
         <v>19.06666666666667</v>
       </c>
-      <c r="AD80" s="56"/>
+      <c r="AD80" s="56">
+        <v>22.2</v>
+      </c>
       <c r="AE80" s="56"/>
       <c r="AF80" s="56"/>
       <c r="AG80" s="56"/>
@@ -15372,11 +15506,11 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>20.564912280701751</v>
+        <v>20.646666666666665</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15384,7 +15518,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>1.2583328517712324</v>
+        <v>1.3400872377361459</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15600,7 +15734,9 @@
       <c r="AE82" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="AF82" s="56"/>
+      <c r="AF82" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="AG82" s="56"/>
       <c r="AH82" s="56"/>
       <c r="AI82" s="56"/>
@@ -15612,11 +15748,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>25.957142857142859</v>
+        <v>26.034848484848485</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15624,7 +15760,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>0.78342039972127964</v>
+        <v>0.86112602742690569</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15861,7 +15997,9 @@
       <c r="AE85" s="56">
         <v>30.55</v>
       </c>
-      <c r="AF85" s="56"/>
+      <c r="AF85" s="56">
+        <v>30.35</v>
+      </c>
       <c r="AG85" s="56"/>
       <c r="AH85" s="56"/>
       <c r="AI85" s="56"/>
@@ -15873,7 +16011,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15982,7 +16120,9 @@
       <c r="AE86" s="56">
         <v>29.3</v>
       </c>
-      <c r="AF86" s="56"/>
+      <c r="AF86" s="56">
+        <v>29.9</v>
+      </c>
       <c r="AG86" s="56"/>
       <c r="AH86" s="56"/>
       <c r="AI86" s="56"/>
@@ -15994,11 +16134,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.747619047619043</v>
+        <v>29.75454545454545</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16006,7 +16146,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1355358860642539</v>
+        <v>1.1424622929906612</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16103,7 +16243,9 @@
       <c r="AE87" s="56">
         <v>30.25</v>
       </c>
-      <c r="AF87" s="56"/>
+      <c r="AF87" s="56">
+        <v>31.25</v>
+      </c>
       <c r="AG87" s="56"/>
       <c r="AH87" s="56"/>
       <c r="AI87" s="56"/>
@@ -16115,11 +16257,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>32.140476190476193</v>
+        <v>32.1</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16127,7 +16269,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>3.134286218013802</v>
+        <v>3.0938100275376108</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16224,7 +16366,9 @@
       <c r="AE88" s="56">
         <v>30.4</v>
       </c>
-      <c r="AF88" s="56"/>
+      <c r="AF88" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AG88" s="56"/>
       <c r="AH88" s="56"/>
       <c r="AI88" s="56"/>
@@ -16236,11 +16380,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.340476190476195</v>
+        <v>30.275000000000002</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16248,7 +16392,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.6496015745007853</v>
+        <v>1.5841253840245919</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16335,7 +16479,9 @@
       <c r="AE89" s="56">
         <v>33</v>
       </c>
-      <c r="AF89" s="56"/>
+      <c r="AF89" s="56">
+        <v>31.25</v>
+      </c>
       <c r="AG89" s="56"/>
       <c r="AH89" s="56"/>
       <c r="AI89" s="56"/>
@@ -16347,11 +16493,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>33.668749999999996</v>
+        <v>33.526470588235291</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16359,7 +16505,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>4.1862509583532947</v>
+        <v>4.0439715465885904</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16686,7 +16832,9 @@
       <c r="AE92" s="56">
         <v>16.850000000000001</v>
       </c>
-      <c r="AF92" s="56"/>
+      <c r="AF92" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="AG92" s="56"/>
       <c r="AH92" s="56"/>
       <c r="AI92" s="56"/>
@@ -16698,11 +16846,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.625396825396827</v>
+        <v>17.624242424242428</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16710,7 +16858,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.4620527393753555</v>
+        <v>1.4608983382209573</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16807,7 +16955,9 @@
       <c r="AE93" s="56">
         <v>23.06666666666667</v>
       </c>
-      <c r="AF93" s="56"/>
+      <c r="AF93" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="AG93" s="56"/>
       <c r="AH93" s="56"/>
       <c r="AI93" s="56"/>
@@ -16819,11 +16969,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.647619047619045</v>
+        <v>23.630303030303029</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16831,7 +16981,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.5381311817494243</v>
+        <v>1.520815164433408</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16928,7 +17078,9 @@
       <c r="AE94" s="56">
         <v>16.2</v>
       </c>
-      <c r="AF94" s="56"/>
+      <c r="AF94" s="56">
+        <v>18.149999999999999</v>
+      </c>
       <c r="AG94" s="56"/>
       <c r="AH94" s="56"/>
       <c r="AI94" s="56"/>
@@ -16940,11 +17092,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.327380952380956</v>
+        <v>17.364772727272729</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16952,7 +17104,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.2321538064463873</v>
+        <v>1.2695455813381606</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17049,7 +17201,9 @@
       <c r="AE95" s="56">
         <v>13.8</v>
       </c>
-      <c r="AF95" s="56"/>
+      <c r="AF95" s="56">
+        <v>15.5</v>
+      </c>
       <c r="AG95" s="56"/>
       <c r="AH95" s="56"/>
       <c r="AI95" s="56"/>
@@ -17061,11 +17215,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.673809523809526</v>
+        <v>14.711363636363638</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17073,7 +17227,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0410013876576656</v>
+        <v>1.0785555002117775</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17328,7 +17482,9 @@
       <c r="AE98" s="56">
         <v>12.5</v>
       </c>
-      <c r="AF98" s="56"/>
+      <c r="AF98" s="56">
+        <v>12.65</v>
+      </c>
       <c r="AG98" s="56"/>
       <c r="AH98" s="56"/>
       <c r="AI98" s="56"/>
@@ -17340,11 +17496,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.238095238095241</v>
+        <v>13.211363636363638</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17445,7 +17601,9 @@
       <c r="AE99" s="56">
         <v>15.133333333333329</v>
       </c>
-      <c r="AF99" s="56"/>
+      <c r="AF99" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="AG99" s="56"/>
       <c r="AH99" s="56"/>
       <c r="AI99" s="56"/>
@@ -17457,11 +17615,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.463157894736844</v>
+        <v>14.453333333333333</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17556,7 +17714,9 @@
       <c r="AE100" s="56">
         <v>16.06666666666667</v>
       </c>
-      <c r="AF100" s="56"/>
+      <c r="AF100" s="56">
+        <v>16.2</v>
+      </c>
       <c r="AG100" s="56"/>
       <c r="AH100" s="56"/>
       <c r="AI100" s="56"/>
@@ -17568,11 +17728,11 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.341666666666669</v>
+        <v>16.333333333333336</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17580,7 +17740,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>2.0323087605586778</v>
+        <v>2.023975427225345</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17667,7 +17827,9 @@
       <c r="AE101" s="56">
         <v>13</v>
       </c>
-      <c r="AF101" s="56"/>
+      <c r="AF101" s="56">
+        <v>14.05</v>
+      </c>
       <c r="AG101" s="56"/>
       <c r="AH101" s="56"/>
       <c r="AI101" s="56"/>
@@ -17679,11 +17841,11 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.521875</v>
+        <v>13.552941176470588</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17691,7 +17853,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.18947133738871</v>
+        <v>1.2205375138592984</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17782,7 +17944,9 @@
       <c r="AE102" s="56">
         <v>11.866666666666671</v>
       </c>
-      <c r="AF102" s="56"/>
+      <c r="AF102" s="56">
+        <v>14.2</v>
+      </c>
       <c r="AG102" s="56"/>
       <c r="AH102" s="56"/>
       <c r="AI102" s="56"/>
@@ -17794,11 +17958,11 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.048148148148151</v>
+        <v>13.108771929824563</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17806,7 +17970,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.8011527787622601</v>
+        <v>1.8617765604386722</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18055,7 +18219,9 @@
       <c r="AE105" s="56">
         <v>20.866666666666671</v>
       </c>
-      <c r="AF105" s="56"/>
+      <c r="AF105" s="56">
+        <v>18</v>
+      </c>
       <c r="AG105" s="56"/>
       <c r="AH105" s="56"/>
       <c r="AI105" s="56"/>
@@ -18067,11 +18233,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.062962962962967</v>
+        <v>18.05964912280702</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18079,7 +18245,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.018425454486696</v>
+        <v>1.015111614330749</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18237,7 +18403,9 @@
       <c r="AE107" s="56">
         <v>14.866666666666671</v>
       </c>
-      <c r="AF107" s="56"/>
+      <c r="AF107" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AG107" s="56"/>
       <c r="AH107" s="56"/>
       <c r="AI107" s="56"/>
@@ -18249,7 +18417,7 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ107" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18358,7 +18526,9 @@
       <c r="AE108" s="56">
         <v>14.85</v>
       </c>
-      <c r="AF108" s="56"/>
+      <c r="AF108" s="56">
+        <v>15.5</v>
+      </c>
       <c r="AG108" s="56"/>
       <c r="AH108" s="56"/>
       <c r="AI108" s="56"/>
@@ -18370,11 +18540,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>13.995238095238097</v>
+        <v>14.063636363636364</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18382,7 +18552,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-0.23379481949371339</v>
+        <v>-0.16539655109544604</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18479,7 +18649,9 @@
       <c r="AE109" s="56">
         <v>14.2</v>
       </c>
-      <c r="AF109" s="56"/>
+      <c r="AF109" s="56">
+        <v>14.9</v>
+      </c>
       <c r="AG109" s="56"/>
       <c r="AH109" s="56"/>
       <c r="AI109" s="56"/>
@@ -18491,11 +18663,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.523809523809522</v>
+        <v>14.540909090909087</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18503,7 +18675,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.81004643630173234</v>
+        <v>0.82714600340129785</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18600,7 +18772,9 @@
       <c r="AE110" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="AF110" s="56"/>
+      <c r="AF110" s="56">
+        <v>17.86666666666666</v>
+      </c>
       <c r="AG110" s="56"/>
       <c r="AH110" s="56"/>
       <c r="AI110" s="56"/>
@@ -18612,11 +18786,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.498412698412693</v>
+        <v>17.515151515151508</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18624,7 +18798,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.56345065994580423</v>
+        <v>0.58018947668461962</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18721,7 +18895,9 @@
       <c r="AE111" s="56">
         <v>15.8</v>
       </c>
-      <c r="AF111" s="56"/>
+      <c r="AF111" s="56">
+        <v>16.56666666666667</v>
+      </c>
       <c r="AG111" s="56"/>
       <c r="AH111" s="56"/>
       <c r="AI111" s="56"/>
@@ -18733,11 +18909,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.939682539682543</v>
+        <v>15.96818181818182</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18745,7 +18921,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.43731901610935431</v>
+        <v>0.46581829460863133</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18842,7 +19018,9 @@
       <c r="AE112" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="AF112" s="56"/>
+      <c r="AF112" s="56">
+        <v>18.333333333333329</v>
+      </c>
       <c r="AG112" s="56"/>
       <c r="AH112" s="56"/>
       <c r="AI112" s="56"/>
@@ -18854,11 +19032,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.825396825396822</v>
+        <v>17.848484848484844</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18866,7 +19044,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4457005642947429</v>
+        <v>1.4687885873827646</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18961,7 +19139,9 @@
       <c r="AE113" s="56">
         <v>19.2</v>
       </c>
-      <c r="AF113" s="56"/>
+      <c r="AF113" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AG113" s="56"/>
       <c r="AH113" s="56"/>
       <c r="AI113" s="56"/>
@@ -18973,11 +19153,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.116666666666667</v>
+        <v>19.149206349206349</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18985,7 +19165,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.99227919911013629</v>
+        <v>1.0248188816498178</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19171,9 +19351,11 @@
         <v>26.25</v>
       </c>
       <c r="AE115" s="56">
-        <v>26.43333333333333</v>
-      </c>
-      <c r="AF115" s="56"/>
+        <v>26.024999999999999</v>
+      </c>
+      <c r="AF115" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AG115" s="56"/>
       <c r="AH115" s="56"/>
       <c r="AI115" s="56"/>
@@ -19185,11 +19367,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.306349206349203</v>
+        <v>26.27840909090909</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19197,7 +19379,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.46186922859618207</v>
+        <v>0.43392911315606852</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19294,7 +19476,9 @@
       <c r="AE116" s="56">
         <v>18.466666666666669</v>
       </c>
-      <c r="AF116" s="56"/>
+      <c r="AF116" s="56">
+        <v>19.93333333333333</v>
+      </c>
       <c r="AG116" s="56"/>
       <c r="AH116" s="56"/>
       <c r="AI116" s="56"/>
@@ -19306,11 +19490,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.196825396825396</v>
+        <v>19.23030303030303</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19318,7 +19502,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.80032023048457646</v>
+        <v>0.83379786396221078</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19415,7 +19599,9 @@
       <c r="AE117" s="56">
         <v>26.866666666666671</v>
       </c>
-      <c r="AF117" s="56"/>
+      <c r="AF117" s="56">
+        <v>26.466666666666669</v>
+      </c>
       <c r="AG117" s="56"/>
       <c r="AH117" s="56"/>
       <c r="AI117" s="56"/>
@@ -19427,11 +19613,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.326984126984133</v>
+        <v>26.333333333333339</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19439,7 +19625,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.95814452124938398</v>
+        <v>0.96449372759859031</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19657,7 +19843,9 @@
       <c r="AE119" s="56">
         <v>24</v>
       </c>
-      <c r="AF119" s="56"/>
+      <c r="AF119" s="56">
+        <v>24.4</v>
+      </c>
       <c r="AG119" s="56"/>
       <c r="AH119" s="56"/>
       <c r="AI119" s="56"/>
@@ -19669,11 +19857,11 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.50476190476191</v>
+        <v>23.54545454545455</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19681,7 +19869,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.7763210445469007</v>
+        <v>1.8170136852395409</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19958,7 +20146,9 @@
       <c r="AE122" s="56">
         <v>12.733333333333331</v>
       </c>
-      <c r="AF122" s="56"/>
+      <c r="AF122" s="56">
+        <v>12.866666666666671</v>
+      </c>
       <c r="AG122" s="56"/>
       <c r="AH122" s="56"/>
       <c r="AI122" s="56"/>
@@ -19970,11 +20160,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.201587301587299</v>
+        <v>12.231818181818181</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19982,7 +20172,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.8988303056170199</v>
+        <v>1.9290611858479014</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20153,8 +20343,12 @@
       <c r="AD124" s="56">
         <v>17.93333333333333</v>
       </c>
-      <c r="AE124" s="56"/>
-      <c r="AF124" s="56"/>
+      <c r="AE124" s="56">
+        <v>17.533333333333331</v>
+      </c>
+      <c r="AF124" s="56">
+        <v>16.8</v>
+      </c>
       <c r="AG124" s="56"/>
       <c r="AH124" s="56"/>
       <c r="AI124" s="56"/>
@@ -20166,11 +20360,11 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>15.814035087719297</v>
+        <v>15.942857142857143</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20178,7 +20372,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.7649761281757872</v>
+        <v>0.89379818331363303</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20340,7 +20534,9 @@
         <v>13.133333333333329</v>
       </c>
       <c r="AE126" s="56"/>
-      <c r="AF126" s="56"/>
+      <c r="AF126" s="56">
+        <v>12.2</v>
+      </c>
       <c r="AG126" s="56"/>
       <c r="AH126" s="56"/>
       <c r="AI126" s="56"/>
@@ -20352,19 +20548,19 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ126" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12.079999999999997</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>10.712446216063739</v>
       </c>
-      <c r="AS126" s="71" t="str">
+      <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.3675537839362573</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20698,7 +20894,9 @@
       <c r="AE130" s="56">
         <v>17.233333333333331</v>
       </c>
-      <c r="AF130" s="56"/>
+      <c r="AF130" s="56">
+        <v>16.7</v>
+      </c>
       <c r="AG130" s="56"/>
       <c r="AH130" s="56"/>
       <c r="AI130" s="56"/>
@@ -20710,11 +20908,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>15.873015873015875</v>
+        <v>15.910606060606062</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20722,7 +20920,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.619773498548426</v>
+        <v>1.6573636861386127</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20819,7 +21017,9 @@
       <c r="AE131" s="56">
         <v>18.850000000000001</v>
       </c>
-      <c r="AF131" s="56"/>
+      <c r="AF131" s="56">
+        <v>18.350000000000001</v>
+      </c>
       <c r="AG131" s="56"/>
       <c r="AH131" s="56"/>
       <c r="AI131" s="56"/>
@@ -20831,11 +21031,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.323809523809523</v>
+        <v>18.325000000000003</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20843,7 +21043,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5309125249055739</v>
+        <v>1.5321030010960541</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21019,7 +21219,9 @@
       <c r="AE133" s="56">
         <v>14.266666666666669</v>
       </c>
-      <c r="AF133" s="56"/>
+      <c r="AF133" s="56">
+        <v>14</v>
+      </c>
       <c r="AG133" s="56"/>
       <c r="AH133" s="56"/>
       <c r="AI133" s="56"/>
@@ -21031,11 +21233,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>14.03968253968254</v>
+        <v>14.037878787878787</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21043,7 +21245,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.4043427650286997</v>
+        <v>1.4025390132249473</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21261,7 +21463,9 @@
       <c r="AE135" s="56">
         <v>20</v>
       </c>
-      <c r="AF135" s="56"/>
+      <c r="AF135" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AG135" s="56"/>
       <c r="AH135" s="56"/>
       <c r="AI135" s="56"/>
@@ -21273,11 +21477,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.828571428571429</v>
+        <v>20.754545454545454</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21285,7 +21489,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>2.1466907911663</v>
+        <v>2.0726648171403248</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21582,7 +21786,9 @@
       <c r="AE138" s="56">
         <v>24.2</v>
       </c>
-      <c r="AF138" s="56"/>
+      <c r="AF138" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="AG138" s="56"/>
       <c r="AH138" s="56"/>
       <c r="AI138" s="56"/>
@@ -21594,11 +21800,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.30793650793651</v>
+        <v>22.324242424242428</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21606,7 +21812,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.2977154105881112</v>
+        <v>2.3140213268940286</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21703,7 +21909,9 @@
       <c r="AE139" s="56">
         <v>14.525</v>
       </c>
-      <c r="AF139" s="56"/>
+      <c r="AF139" s="56">
+        <v>14.15</v>
+      </c>
       <c r="AG139" s="56"/>
       <c r="AH139" s="56"/>
       <c r="AI139" s="56"/>
@@ -21715,11 +21923,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.076190476190474</v>
+        <v>14.079545454545451</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21727,7 +21935,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.1719727033564649</v>
+        <v>1.1753276817114422</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21824,7 +22032,9 @@
       <c r="AE140" s="56">
         <v>15.4</v>
       </c>
-      <c r="AF140" s="56"/>
+      <c r="AF140" s="56">
+        <v>15.95</v>
+      </c>
       <c r="AG140" s="56"/>
       <c r="AH140" s="56"/>
       <c r="AI140" s="56"/>
@@ -21836,11 +22046,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.557142857142857</v>
+        <v>16.529545454545453</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21848,7 +22058,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.96279228537293626</v>
+        <v>0.93519488277553187</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21945,7 +22155,9 @@
       <c r="AE141" s="56">
         <v>13.8</v>
       </c>
-      <c r="AF141" s="56"/>
+      <c r="AF141" s="56">
+        <v>13.866666666666671</v>
+      </c>
       <c r="AG141" s="56"/>
       <c r="AH141" s="56"/>
       <c r="AI141" s="56"/>
@@ -21957,11 +22169,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.596825396825398</v>
+        <v>13.609090909090911</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21969,7 +22181,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.5827959999873489</v>
+        <v>1.5950615122528617</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22185,7 +22397,9 @@
       <c r="AE143" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="AF143" s="56"/>
+      <c r="AF143" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AG143" s="56"/>
       <c r="AH143" s="56"/>
       <c r="AI143" s="56"/>
@@ -22197,11 +22411,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.723809523809521</v>
+        <v>27.681818181818176</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22209,7 +22423,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.8618694316436404</v>
+        <v>1.8198780896522955</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22306,7 +22520,9 @@
       <c r="AE144" s="56">
         <v>15</v>
       </c>
-      <c r="AF144" s="56"/>
+      <c r="AF144" s="56">
+        <v>16.266666666666669</v>
+      </c>
       <c r="AG144" s="56"/>
       <c r="AH144" s="56"/>
       <c r="AI144" s="56"/>
@@ -22318,11 +22534,11 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>15.593650793650795</v>
+        <v>15.624242424242425</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22330,7 +22546,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>-0.11923496026349412</v>
+        <v>-8.8643329671864279E-2</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22427,7 +22643,9 @@
       <c r="AE145" s="56">
         <v>19.666666666666671</v>
       </c>
-      <c r="AF145" s="56"/>
+      <c r="AF145" s="56">
+        <v>20.8</v>
+      </c>
       <c r="AG145" s="56"/>
       <c r="AH145" s="56"/>
       <c r="AI145" s="56"/>
@@ -22439,11 +22657,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.393650793650792</v>
+        <v>19.457575757575757</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22451,7 +22669,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.35163425915267155</v>
+        <v>0.41555922307763637</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22669,7 +22887,9 @@
       <c r="AE147" s="56">
         <v>24.6</v>
       </c>
-      <c r="AF147" s="56"/>
+      <c r="AF147" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AG147" s="56"/>
       <c r="AH147" s="56"/>
       <c r="AI147" s="56"/>
@@ -22681,11 +22901,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.079365079365083</v>
+        <v>25.151515151515152</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22693,7 +22913,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.5753075875017224</v>
+        <v>1.647457659651792</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22786,7 +23006,9 @@
       <c r="AE148" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="AF148" s="56"/>
+      <c r="AF148" s="56">
+        <v>30</v>
+      </c>
       <c r="AG148" s="56"/>
       <c r="AH148" s="56"/>
       <c r="AI148" s="56"/>
@@ -22798,11 +23020,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.392982456140352</v>
+        <v>30.373333333333335</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22810,7 +23032,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.751451225285571</v>
+        <v>1.7318021024785537</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22907,7 +23129,9 @@
       <c r="AE149" s="56">
         <v>23.733333333333331</v>
       </c>
-      <c r="AF149" s="56"/>
+      <c r="AF149" s="56">
+        <v>23.13333333333334</v>
+      </c>
       <c r="AG149" s="56"/>
       <c r="AH149" s="56"/>
       <c r="AI149" s="56"/>
@@ -22919,11 +23143,11 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.68888888888889</v>
+        <v>23.663636363636364</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22931,7 +23155,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.812821115936039</v>
+        <v>1.787568590683513</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23104,8 +23328,12 @@
       <c r="AD151" s="56">
         <v>21.733333333333331</v>
       </c>
-      <c r="AE151" s="56"/>
-      <c r="AF151" s="56"/>
+      <c r="AE151" s="56">
+        <v>23.333333333333329</v>
+      </c>
+      <c r="AF151" s="56">
+        <v>23.2</v>
+      </c>
       <c r="AG151" s="56"/>
       <c r="AH151" s="56"/>
       <c r="AI151" s="56"/>
@@ -23117,11 +23345,11 @@
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.445</v>
+        <v>23.428787878787876</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23129,7 +23357,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.6324127213793602</v>
+        <v>1.616200600167236</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23384,7 +23612,9 @@
       <c r="AE154" s="56">
         <v>20.350000000000001</v>
       </c>
-      <c r="AF154" s="56"/>
+      <c r="AF154" s="56">
+        <v>20</v>
+      </c>
       <c r="AG154" s="56"/>
       <c r="AH154" s="56"/>
       <c r="AI154" s="56"/>
@@ -23396,11 +23626,11 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.561904761904763</v>
+        <v>20.536363636363639</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23408,7 +23638,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>1.0482840075098245</v>
+        <v>1.0227428819686999</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23505,7 +23735,9 @@
       <c r="AE155" s="56">
         <v>27.2</v>
       </c>
-      <c r="AF155" s="56"/>
+      <c r="AF155" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="AG155" s="56"/>
       <c r="AH155" s="56"/>
       <c r="AI155" s="56"/>
@@ -23517,11 +23749,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>29.082539682539682</v>
+        <v>29.054545454545458</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23529,7 +23761,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.3597531216838838</v>
+        <v>1.3317588936896598</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23697,7 +23929,9 @@
       <c r="AE157" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="AF157" s="56"/>
+      <c r="AF157" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AG157" s="56"/>
       <c r="AH157" s="56"/>
       <c r="AI157" s="56"/>
@@ -23709,11 +23943,11 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.549019607843139</v>
+        <v>29.529629629629635</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23721,7 +23955,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.9645921112337383</v>
+        <v>1.9452021330202349</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23811,7 +24045,9 @@
       <c r="AD158" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="AE158" s="56"/>
+      <c r="AE158" s="56">
+        <v>28.06666666666667</v>
+      </c>
       <c r="AF158" s="56"/>
       <c r="AG158" s="56"/>
       <c r="AH158" s="56"/>
@@ -23824,11 +24060,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.340740740740742</v>
+        <v>30.221052631578949</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23836,7 +24072,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>2.3223285736605419</v>
+        <v>2.2026404644987494</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23927,7 +24163,9 @@
       <c r="AE159" s="56">
         <v>19.466666666666669</v>
       </c>
-      <c r="AF159" s="56"/>
+      <c r="AF159" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AG159" s="56"/>
       <c r="AH159" s="56"/>
       <c r="AI159" s="56"/>
@@ -23939,11 +24177,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.462962962962965</v>
+        <v>20.449122807017545</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23951,7 +24189,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.4720258482725654</v>
+        <v>1.4581856923271452</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24048,7 +24286,9 @@
       <c r="AE160" s="56">
         <v>25.6</v>
       </c>
-      <c r="AF160" s="56"/>
+      <c r="AF160" s="56">
+        <v>27.266666666666669</v>
+      </c>
       <c r="AG160" s="56"/>
       <c r="AH160" s="56"/>
       <c r="AI160" s="56"/>
@@ -24060,11 +24300,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.073015873015883</v>
+        <v>27.081818181818189</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24270,7 +24510,9 @@
       <c r="AE162" s="56">
         <v>28.266666666666669</v>
       </c>
-      <c r="AF162" s="56"/>
+      <c r="AF162" s="56">
+        <v>28.933333333333341</v>
+      </c>
       <c r="AG162" s="56"/>
       <c r="AH162" s="56"/>
       <c r="AI162" s="56"/>
@@ -24282,11 +24524,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>29.028571428571436</v>
+        <v>29.024242424242434</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24294,7 +24536,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.45503404069715714</v>
+        <v>0.45070503636815573</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24391,7 +24633,9 @@
       <c r="AE163" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="AF163" s="56"/>
+      <c r="AF163" s="56">
+        <v>21.266666666666669</v>
+      </c>
       <c r="AG163" s="56"/>
       <c r="AH163" s="56"/>
       <c r="AI163" s="56"/>
@@ -24403,11 +24647,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.457142857142856</v>
+        <v>21.448484848484846</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24415,7 +24659,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.20771904154227627</v>
+        <v>0.19906103288426635</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24512,7 +24756,9 @@
       <c r="AE164" s="56">
         <v>23.1</v>
       </c>
-      <c r="AF164" s="56"/>
+      <c r="AF164" s="56">
+        <v>26</v>
+      </c>
       <c r="AG164" s="56"/>
       <c r="AH164" s="56"/>
       <c r="AI164" s="56"/>
@@ -24524,11 +24770,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.390476190476193</v>
+        <v>25.418181818181822</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24536,7 +24782,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.5925485813161124</v>
+        <v>1.6202542090217413</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24708,7 +24954,9 @@
       <c r="AE166" s="56">
         <v>14.46666666666667</v>
       </c>
-      <c r="AF166" s="56"/>
+      <c r="AF166" s="56">
+        <v>16</v>
+      </c>
       <c r="AG166" s="56"/>
       <c r="AH166" s="56"/>
       <c r="AI166" s="56"/>
@@ -24720,11 +24968,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.908771929824564</v>
+        <v>14.963333333333335</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24732,7 +24980,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.3103023957744231</v>
+        <v>1.364863799283194</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24825,7 +25073,9 @@
       <c r="AE167" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="AF167" s="56"/>
+      <c r="AF167" s="56">
+        <v>20.8</v>
+      </c>
       <c r="AG167" s="56"/>
       <c r="AH167" s="56"/>
       <c r="AI167" s="56"/>
@@ -24837,11 +25087,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.726315789473684</v>
+        <v>20.73</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24849,7 +25099,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.690747979863044</v>
+        <v>1.6944321903893602</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24942,7 +25192,9 @@
       <c r="AE168" s="56">
         <v>26.4</v>
       </c>
-      <c r="AF168" s="56"/>
+      <c r="AF168" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AG168" s="56"/>
       <c r="AH168" s="56"/>
       <c r="AI168" s="56"/>
@@ -24954,11 +25206,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.981578947368419</v>
+        <v>27.942500000000003</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24966,7 +25218,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.9157144813018405</v>
+        <v>1.876635533933424</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25063,7 +25315,9 @@
       <c r="AE169" s="56">
         <v>9.5500000000000007</v>
       </c>
-      <c r="AF169" s="56"/>
+      <c r="AF169" s="56">
+        <v>10.45</v>
+      </c>
       <c r="AG169" s="56"/>
       <c r="AH169" s="56"/>
       <c r="AI169" s="56"/>
@@ -25075,11 +25329,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>8.8809523809523814</v>
+        <v>8.9522727272727263</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25087,7 +25341,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.3388280995978441</v>
+        <v>0.410148445918189</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25168,7 +25422,9 @@
       <c r="AE170" s="56">
         <v>25</v>
       </c>
-      <c r="AF170" s="56"/>
+      <c r="AF170" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AG170" s="56"/>
       <c r="AH170" s="56"/>
       <c r="AI170" s="56"/>
@@ -25180,7 +25436,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -25287,7 +25543,9 @@
       <c r="AE171" s="56">
         <v>21.06666666666667</v>
       </c>
-      <c r="AF171" s="56"/>
+      <c r="AF171" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AG171" s="56"/>
       <c r="AH171" s="56"/>
       <c r="AI171" s="56"/>
@@ -25299,11 +25557,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.900000000000002</v>
+        <v>20.88571428571429</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25311,7 +25569,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.9710739777480839</v>
+        <v>1.9567882634623714</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25404,7 +25662,9 @@
       <c r="AE172" s="56">
         <v>26.8</v>
       </c>
-      <c r="AF172" s="56"/>
+      <c r="AF172" s="56">
+        <v>26.7</v>
+      </c>
       <c r="AG172" s="56"/>
       <c r="AH172" s="56"/>
       <c r="AI172" s="56"/>
@@ -25416,11 +25676,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.644736842105264</v>
+        <v>25.697500000000002</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25428,7 +25688,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2061084735933854</v>
+        <v>1.2588716314881232</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25525,7 +25785,9 @@
       <c r="AE173" s="56">
         <v>24.9</v>
       </c>
-      <c r="AF173" s="56"/>
+      <c r="AF173" s="56">
+        <v>25.85</v>
+      </c>
       <c r="AG173" s="56"/>
       <c r="AH173" s="56"/>
       <c r="AI173" s="56"/>
@@ -25537,11 +25799,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.133730158730163</v>
+        <v>25.166287878787884</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25549,7 +25811,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0793215565796324</v>
+        <v>1.1118792766373531</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25644,7 +25906,9 @@
       <c r="AE174" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="AF174" s="56"/>
+      <c r="AF174" s="56">
+        <v>15.46666666666667</v>
+      </c>
       <c r="AG174" s="56"/>
       <c r="AH174" s="56"/>
       <c r="AI174" s="56"/>
@@ -25656,11 +25920,11 @@
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.810000000000002</v>
+        <v>13.888888888888893</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25668,7 +25932,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.7492481423281419</v>
+        <v>1.8281370312170324</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25714,7 +25978,9 @@
       <c r="N175" s="56">
         <v>24.8</v>
       </c>
-      <c r="O175" s="56"/>
+      <c r="O175" s="56">
+        <v>25.8</v>
+      </c>
       <c r="P175" s="56"/>
       <c r="Q175" s="56">
         <v>26.4</v>
@@ -25734,20 +26000,34 @@
       <c r="V175" s="56">
         <v>23.6</v>
       </c>
-      <c r="W175" s="56"/>
-      <c r="X175" s="56"/>
-      <c r="Y175" s="56"/>
-      <c r="Z175" s="56"/>
-      <c r="AA175" s="56"/>
+      <c r="W175" s="56">
+        <v>24.333333333333329</v>
+      </c>
+      <c r="X175" s="56">
+        <v>24.6</v>
+      </c>
+      <c r="Y175" s="56">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="Z175" s="56">
+        <v>24.86666666666666</v>
+      </c>
+      <c r="AA175" s="56">
+        <v>25.266666666666669</v>
+      </c>
       <c r="AB175" s="56"/>
-      <c r="AC175" s="56"/>
+      <c r="AC175" s="56">
+        <v>23.4</v>
+      </c>
       <c r="AD175" s="56">
         <v>24.533333333333331</v>
       </c>
       <c r="AE175" s="56">
         <v>23.533333333333331</v>
       </c>
-      <c r="AF175" s="56"/>
+      <c r="AF175" s="56">
+        <v>24.4</v>
+      </c>
       <c r="AG175" s="56"/>
       <c r="AH175" s="56"/>
       <c r="AI175" s="56"/>
@@ -25759,19 +26039,19 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AQ175" s="71" t="str">
+        <v>20</v>
+      </c>
+      <c r="AQ175" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>24.711666666666662</v>
       </c>
       <c r="AR175" s="71">
         <f>IFERROR(VLOOKUP(A175,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.532893345747048</v>
       </c>
-      <c r="AS175" s="71" t="str">
+      <c r="AS175" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.1787733209196141</v>
       </c>
     </row>
     <row r="176" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26016,7 +26296,9 @@
       <c r="AE178" s="56">
         <v>24.066666666666659</v>
       </c>
-      <c r="AF178" s="56"/>
+      <c r="AF178" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AG178" s="56"/>
       <c r="AH178" s="56"/>
       <c r="AI178" s="56"/>
@@ -26028,11 +26310,11 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.291666666666664</v>
+        <v>25.286274509803917</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26040,7 +26322,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.73938631978777281</v>
+        <v>0.73399416292502551</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26129,7 +26411,9 @@
       <c r="AE179" s="56">
         <v>18.55</v>
       </c>
-      <c r="AF179" s="56"/>
+      <c r="AF179" s="56">
+        <v>19.05</v>
+      </c>
       <c r="AG179" s="56"/>
       <c r="AH179" s="56"/>
       <c r="AI179" s="56"/>
@@ -26141,11 +26425,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.761764705882353</v>
+        <v>18.777777777777779</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26153,7 +26437,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>1.1741810223657012</v>
+        <v>1.1901940942611269</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26329,7 +26613,9 @@
       <c r="AE181" s="56">
         <v>29.733333333333331</v>
       </c>
-      <c r="AF181" s="56"/>
+      <c r="AF181" s="56">
+        <v>32.4</v>
+      </c>
       <c r="AG181" s="56"/>
       <c r="AH181" s="56"/>
       <c r="AI181" s="56"/>
@@ -26341,11 +26627,11 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.87619047619047</v>
+        <v>30.945454545454538</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26353,7 +26639,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.3429540886206581</v>
+        <v>2.4122181578847268</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26608,7 +26894,9 @@
       <c r="AE184" s="56">
         <v>28.8</v>
       </c>
-      <c r="AF184" s="56"/>
+      <c r="AF184" s="56">
+        <v>28.93333333333333</v>
+      </c>
       <c r="AG184" s="56"/>
       <c r="AH184" s="56"/>
       <c r="AI184" s="56"/>
@@ -26620,11 +26908,11 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.028571428571428</v>
+        <v>28.069696969696967</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26632,7 +26920,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.3902002109544398</v>
+        <v>1.431325752079978</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26721,7 +27009,9 @@
       <c r="AE185" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="AF185" s="56"/>
+      <c r="AF185" s="56">
+        <v>30.733333333333331</v>
+      </c>
       <c r="AG185" s="56"/>
       <c r="AH185" s="56"/>
       <c r="AI185" s="56"/>
@@ -26733,11 +27023,11 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.827450980392157</v>
+        <v>28.93333333333333</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26745,7 +27035,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.2188186953807865</v>
+        <v>1.324701048321959</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27000,7 +27290,9 @@
       <c r="AE188" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AF188" s="56"/>
+      <c r="AF188" s="56">
+        <v>17.93333333333333</v>
+      </c>
       <c r="AG188" s="56"/>
       <c r="AH188" s="56"/>
       <c r="AI188" s="56"/>
@@ -27012,11 +27304,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.431746031746037</v>
+        <v>17.45454545454546</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27024,7 +27316,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.4361540422143069</v>
+        <v>1.4589534650137299</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27109,7 +27401,9 @@
         <v>30.06666666666667</v>
       </c>
       <c r="AE189" s="56"/>
-      <c r="AF189" s="56"/>
+      <c r="AF189" s="56">
+        <v>33.266666666666673</v>
+      </c>
       <c r="AG189" s="56"/>
       <c r="AH189" s="56"/>
       <c r="AI189" s="56"/>
@@ -27121,11 +27415,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>32.155555555555559</v>
+        <v>32.225000000000009</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27133,7 +27427,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>2.3039711975027686</v>
+        <v>2.3734156419472185</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27227,8 +27521,12 @@
       <c r="AD190" s="56">
         <v>32.06666666666667</v>
       </c>
-      <c r="AE190" s="56"/>
-      <c r="AF190" s="56"/>
+      <c r="AE190" s="56">
+        <v>28.93333333333333</v>
+      </c>
+      <c r="AF190" s="56">
+        <v>30.933333333333341</v>
+      </c>
       <c r="AG190" s="56"/>
       <c r="AH190" s="56"/>
       <c r="AI190" s="56"/>
@@ -27240,11 +27538,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.81333333333334</v>
+        <v>30.733333333333338</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27252,7 +27550,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.8968096718508711</v>
+        <v>1.8168096718508693</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27349,7 +27647,9 @@
       <c r="AE191" s="56">
         <v>18.649999999999999</v>
       </c>
-      <c r="AF191" s="56"/>
+      <c r="AF191" s="56">
+        <v>19.149999999999999</v>
+      </c>
       <c r="AG191" s="56"/>
       <c r="AH191" s="56"/>
       <c r="AI191" s="56"/>
@@ -27361,11 +27661,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.707142857142856</v>
+        <v>18.727272727272723</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27373,7 +27673,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.3199238424822468</v>
+        <v>1.3400537126121144</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27470,7 +27770,9 @@
       <c r="AE192" s="56">
         <v>26.6</v>
       </c>
-      <c r="AF192" s="56"/>
+      <c r="AF192" s="56">
+        <v>26.13333333333334</v>
+      </c>
       <c r="AG192" s="56"/>
       <c r="AH192" s="56"/>
       <c r="AI192" s="56"/>
@@ -27482,11 +27784,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.104761904761911</v>
+        <v>26.106060606060613</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27494,7 +27796,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.86025472394373992</v>
+        <v>0.86155342524244105</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27706,7 +28008,9 @@
       <c r="AE194" s="56">
         <v>20.133333333333329</v>
       </c>
-      <c r="AF194" s="56"/>
+      <c r="AF194" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="AG194" s="56"/>
       <c r="AH194" s="56"/>
       <c r="AI194" s="56"/>
@@ -27718,11 +28022,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.174603174603174</v>
+        <v>21.242424242424246</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27730,7 +28034,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.43305862245525617</v>
+        <v>-0.36523755463418439</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27827,7 +28131,9 @@
       <c r="AE195" s="56">
         <v>25.666666666666671</v>
       </c>
-      <c r="AF195" s="56"/>
+      <c r="AF195" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="AG195" s="56"/>
       <c r="AH195" s="56"/>
       <c r="AI195" s="56"/>
@@ -27839,11 +28145,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.968253968253965</v>
+        <v>27.930303030303026</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27851,7 +28157,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>2.2807657585442058</v>
+        <v>2.2428148205932672</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27948,7 +28254,9 @@
       <c r="AE196" s="56">
         <v>20.466666666666669</v>
       </c>
-      <c r="AF196" s="56"/>
+      <c r="AF196" s="56">
+        <v>22.4</v>
+      </c>
       <c r="AG196" s="56"/>
       <c r="AH196" s="56"/>
       <c r="AI196" s="56"/>
@@ -27960,11 +28268,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.323809523809526</v>
+        <v>22.327272727272728</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27972,7 +28280,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>2.100053052284256</v>
+        <v>2.1035162557474578</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28069,7 +28377,9 @@
       <c r="AE197" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="AF197" s="56"/>
+      <c r="AF197" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AG197" s="56"/>
       <c r="AH197" s="56"/>
       <c r="AI197" s="56"/>
@@ -28081,11 +28391,11 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.898412698412692</v>
+        <v>25.957575757575754</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28093,7 +28403,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.7710296972421631</v>
+        <v>1.8301927564052249</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28190,7 +28500,9 @@
       <c r="AE198" s="56">
         <v>21.65</v>
       </c>
-      <c r="AF198" s="56"/>
+      <c r="AF198" s="56">
+        <v>21.45</v>
+      </c>
       <c r="AG198" s="56"/>
       <c r="AH198" s="56"/>
       <c r="AI198" s="56"/>
@@ -28202,11 +28514,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.699999999999996</v>
+        <v>21.688636363636359</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28308,8 +28620,12 @@
       <c r="AD199" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="AE199" s="56"/>
-      <c r="AF199" s="56"/>
+      <c r="AE199" s="56">
+        <v>16.333333333333329</v>
+      </c>
+      <c r="AF199" s="56">
+        <v>16.866666666666671</v>
+      </c>
       <c r="AG199" s="56"/>
       <c r="AH199" s="56"/>
       <c r="AI199" s="56"/>
@@ -28321,11 +28637,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.64</v>
+        <v>16.636363636363637</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28333,7 +28649,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.85233959380881075</v>
+        <v>0.84870323017244687</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28430,7 +28746,9 @@
       <c r="AE200" s="56">
         <v>14.5</v>
       </c>
-      <c r="AF200" s="56"/>
+      <c r="AF200" s="56">
+        <v>15.65</v>
+      </c>
       <c r="AG200" s="56"/>
       <c r="AH200" s="56"/>
       <c r="AI200" s="56"/>
@@ -28442,11 +28760,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.723809523809528</v>
+        <v>14.765909090909094</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28454,7 +28772,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.3581970560258885</v>
+        <v>1.4002966231254543</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28551,7 +28869,9 @@
       <c r="AE201" s="56">
         <v>27.4</v>
       </c>
-      <c r="AF201" s="56"/>
+      <c r="AF201" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AG201" s="56"/>
       <c r="AH201" s="56"/>
       <c r="AI201" s="56"/>
@@ -28563,11 +28883,11 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>27.178571428571423</v>
+        <v>27.270454545454541</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28575,7 +28895,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.6410421602405734</v>
+        <v>1.7329252771236909</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28660,7 +28980,9 @@
       <c r="AE202" s="56">
         <v>12.6</v>
       </c>
-      <c r="AF202" s="56"/>
+      <c r="AF202" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AG202" s="56"/>
       <c r="AH202" s="56"/>
       <c r="AI202" s="56"/>
@@ -28672,11 +28994,11 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ202" s="71">
         <f t="shared" si="10"/>
-        <v>13.54</v>
+        <v>13.606249999999999</v>
       </c>
       <c r="AR202" s="71">
         <f>IFERROR(VLOOKUP(A202,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28684,7 +29006,7 @@
       </c>
       <c r="AS202" s="71">
         <f t="shared" si="11"/>
-        <v>0.73643604149607889</v>
+        <v>0.80268604149607903</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28777,7 +29099,9 @@
       <c r="AE203" s="56">
         <v>14.2</v>
       </c>
-      <c r="AF203" s="56"/>
+      <c r="AF203" s="56">
+        <v>15.2</v>
+      </c>
       <c r="AG203" s="56"/>
       <c r="AH203" s="56"/>
       <c r="AI203" s="56"/>
@@ -28789,11 +29113,11 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v>14.063157894736841</v>
+        <v>14.12</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28801,7 +29125,7 @@
       </c>
       <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v>2.0922830442558009</v>
+        <v>2.1491251495189587</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29115,8 +29439,12 @@
       <c r="AD206" s="56">
         <v>13.2</v>
       </c>
-      <c r="AE206" s="56"/>
-      <c r="AF206" s="56"/>
+      <c r="AE206" s="56">
+        <v>14.75</v>
+      </c>
+      <c r="AF206" s="56">
+        <v>13.75</v>
+      </c>
       <c r="AG206" s="56"/>
       <c r="AH206" s="56"/>
       <c r="AI206" s="56"/>
@@ -29128,11 +29456,11 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v>13.478947368421053</v>
+        <v>13.552380952380954</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29223,7 +29551,9 @@
       <c r="AE207" s="56">
         <v>14.93333333333333</v>
       </c>
-      <c r="AF207" s="56"/>
+      <c r="AF207" s="56">
+        <v>14.2</v>
+      </c>
       <c r="AG207" s="56"/>
       <c r="AH207" s="56"/>
       <c r="AI207" s="56"/>
@@ -29235,19 +29565,19 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ207" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>14.293333333333331</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.56077580506272</v>
       </c>
-      <c r="AS207" s="71" t="str">
+      <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.73255752827061116</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29342,7 +29672,9 @@
       <c r="AE208" s="56">
         <v>14.7</v>
       </c>
-      <c r="AF208" s="56"/>
+      <c r="AF208" s="56">
+        <v>14.15</v>
+      </c>
       <c r="AG208" s="56"/>
       <c r="AH208" s="56"/>
       <c r="AI208" s="56"/>
@@ -29354,11 +29686,11 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.41</v>
+        <v>14.397619047619045</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29463,7 +29795,9 @@
       <c r="AE209" s="56">
         <v>10.75</v>
       </c>
-      <c r="AF209" s="56"/>
+      <c r="AF209" s="56">
+        <v>11.05</v>
+      </c>
       <c r="AG209" s="56"/>
       <c r="AH209" s="56"/>
       <c r="AI209" s="56"/>
@@ -29475,11 +29809,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.045238095238096</v>
+        <v>11.045454545454547</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29584,7 +29918,9 @@
       <c r="AE210" s="56">
         <v>15.55</v>
       </c>
-      <c r="AF210" s="56"/>
+      <c r="AF210" s="56">
+        <v>16.45</v>
+      </c>
       <c r="AG210" s="56"/>
       <c r="AH210" s="56"/>
       <c r="AI210" s="56"/>
@@ -29596,11 +29932,11 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v>15.754761904761907</v>
+        <v>15.786363636363637</v>
       </c>
       <c r="AR210" s="71">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29608,7 +29944,7 @@
       </c>
       <c r="AS210" s="71">
         <f t="shared" si="11"/>
-        <v>1.4250916994779761</v>
+        <v>1.4566934310797066</v>
       </c>
     </row>
     <row r="211" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29705,7 +30041,9 @@
       <c r="AE211" s="56">
         <v>8.3000000000000007</v>
       </c>
-      <c r="AF211" s="56"/>
+      <c r="AF211" s="56">
+        <v>8.85</v>
+      </c>
       <c r="AG211" s="56"/>
       <c r="AH211" s="56"/>
       <c r="AI211" s="56"/>
@@ -29717,11 +30055,11 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.6666666666666661</v>
+        <v>8.6749999999999989</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29729,7 +30067,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.5865337849762664</v>
+        <v>0.59486711830959926</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29854,6 +30192,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="AF1:AF212" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K5:AO212">
     <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>""</formula>
